--- a/docs/XP团角色卡模板.xlsx
+++ b/docs/XP团角色卡模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xp-wiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BB6C6B-8894-4B52-BF5D-2F0BE192D6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66801DB7-C410-4248-9343-AC5BF9046A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,7 +546,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="407">
   <si>
     <t>角色基础信息</t>
   </si>
@@ -1517,21 +1517,12 @@
     <t>坐骑防具</t>
   </si>
   <si>
-    <t>矮脚马</t>
-  </si>
-  <si>
     <t>马</t>
   </si>
   <si>
     <t>性能阈值</t>
   </si>
   <si>
-    <t>性能加成</t>
-  </si>
-  <si>
-    <t>机动加成</t>
-  </si>
-  <si>
     <t>性能</t>
   </si>
   <si>
@@ -1566,15 +1557,6 @@
   </si>
   <si>
     <t>坐骑体力（HP）</t>
-  </si>
-  <si>
-    <t>骑乘状态行动点（AP）</t>
-  </si>
-  <si>
-    <t>骑乘者基础行动点</t>
-  </si>
-  <si>
-    <t>坐骑行动点</t>
   </si>
   <si>
     <t>范围1格内有2名队友时，你防御的检定阈值附加战术奖励，最多叠加1层（不可叠加）</t>
@@ -1849,6 +1831,14 @@
   </si>
   <si>
     <t>锻造、灵知</t>
+    <phoneticPr fontId="47" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通战马</t>
+    <phoneticPr fontId="47" type="noConversion"/>
+  </si>
+  <si>
+    <t>经历点额外</t>
     <phoneticPr fontId="47" type="noConversion"/>
   </si>
 </sst>
@@ -3024,7 +3014,7 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3429,12 +3419,6 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3463,6 +3447,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3764,6 +3754,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -6118,7 +6111,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{484681FD-25D8-41EF-8186-EBB82823EA17}" type="CELLRANGE">
+                    <a:fld id="{9DA856AC-5452-407A-9182-E8BB30FDB752}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6127,7 +6120,7 @@
                       <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{BA3D425C-D489-468B-9864-D6A2A94D7E53}" type="VALUE">
+                    <a:fld id="{89ECCFC3-3934-4977-8305-81F75A5DAE03}" type="VALUE">
                       <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[值]</a:t>
@@ -6291,7 +6284,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F41F6460-85F4-491B-BB98-2951A107C088}" type="CELLRANGE">
+                    <a:fld id="{53186B57-347E-4FAA-9199-38089AB7FB25}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6300,7 +6293,7 @@
                       <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{38828250-1D6B-4440-900E-0E750963055A}" type="VALUE">
+                    <a:fld id="{16989473-7F63-43A6-9DB8-917CDE566528}" type="VALUE">
                       <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[值]</a:t>
@@ -9193,7 +9186,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{23379E4D-A631-47AC-96D4-8E995D843D41}" type="CELLRANGE">
+                    <a:fld id="{2DF83497-F236-470F-916E-80B17C61C727}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9202,7 +9195,7 @@
                       <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{C7865CAF-C061-449F-9680-5931CA78345B}" type="VALUE">
+                    <a:fld id="{55AB5F9A-8730-4E96-A752-467E84E948D9}" type="VALUE">
                       <a:rPr lang="zh-CN" altLang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[值]</a:t>
@@ -15310,28 +15303,28 @@
         <v>116</v>
       </c>
       <c r="C5" s="207" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D5" s="208"/>
       <c r="E5" s="208"/>
       <c r="F5" s="208"/>
       <c r="G5" s="209"/>
       <c r="H5" s="213" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="I5" s="167"/>
       <c r="J5" s="167"/>
       <c r="K5" s="167"/>
       <c r="L5" s="168"/>
       <c r="M5" s="166" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="N5" s="167"/>
       <c r="O5" s="167"/>
       <c r="P5" s="167"/>
       <c r="Q5" s="168"/>
       <c r="R5" s="166" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="S5" s="167"/>
       <c r="T5" s="167"/>
@@ -15370,21 +15363,21 @@
         <v>116</v>
       </c>
       <c r="C7" s="215" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D7" s="208"/>
       <c r="E7" s="208"/>
       <c r="F7" s="208"/>
       <c r="G7" s="209"/>
       <c r="H7" s="213" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="I7" s="167"/>
       <c r="J7" s="167"/>
       <c r="K7" s="167"/>
       <c r="L7" s="168"/>
       <c r="M7" s="213" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="N7" s="167"/>
       <c r="O7" s="167"/>
@@ -15430,28 +15423,28 @@
         <v>116</v>
       </c>
       <c r="C9" s="207" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D9" s="208"/>
       <c r="E9" s="208"/>
       <c r="F9" s="208"/>
       <c r="G9" s="209"/>
       <c r="H9" s="213" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="I9" s="167"/>
       <c r="J9" s="167"/>
       <c r="K9" s="167"/>
       <c r="L9" s="168"/>
       <c r="M9" s="166" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="N9" s="167"/>
       <c r="O9" s="167"/>
       <c r="P9" s="167"/>
       <c r="Q9" s="168"/>
       <c r="R9" s="166" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="S9" s="167"/>
       <c r="T9" s="167"/>
@@ -15490,28 +15483,28 @@
         <v>116</v>
       </c>
       <c r="C11" s="215" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D11" s="208"/>
       <c r="E11" s="208"/>
       <c r="F11" s="208"/>
       <c r="G11" s="209"/>
       <c r="H11" s="166" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="I11" s="167"/>
       <c r="J11" s="167"/>
       <c r="K11" s="167"/>
       <c r="L11" s="168"/>
       <c r="M11" s="166" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="N11" s="167"/>
       <c r="O11" s="167"/>
       <c r="P11" s="167"/>
       <c r="Q11" s="168"/>
       <c r="R11" s="166" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="S11" s="167"/>
       <c r="T11" s="167"/>
@@ -17803,7 +17796,7 @@
       </c>
       <c r="C2" s="108"/>
       <c r="D2" s="11" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E2" s="12">
         <v>7</v>
@@ -17839,7 +17832,7 @@
     </row>
     <row r="3" spans="1:32" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B3" s="63" t="str">
         <f ca="1">AC1 &amp; "通"</f>
@@ -17850,10 +17843,10 @@
         <v>8贯</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>313</v>
@@ -17862,10 +17855,10 @@
         <v>314</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="K3" s="235" t="s">
         <v>96</v>
@@ -17906,32 +17899,32 @@
       <c r="C4" s="240"/>
       <c r="D4" s="240"/>
       <c r="E4" s="240"/>
-      <c r="G4" s="137" t="s">
+      <c r="G4" s="135" t="s">
         <v>317</v>
       </c>
-      <c r="H4" s="137">
+      <c r="H4" s="135">
         <v>4</v>
       </c>
-      <c r="I4" s="137">
+      <c r="I4" s="135">
         <v>1</v>
       </c>
-      <c r="J4" s="137">
+      <c r="J4" s="135">
         <v>7</v>
       </c>
-      <c r="K4" s="137" t="s">
+      <c r="K4" s="135" t="s">
         <v>318</v>
       </c>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
       <c r="P4" s="234" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
+        <v>361</v>
+      </c>
+      <c r="Q4" s="135"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="135"/>
+      <c r="T4" s="135"/>
       <c r="U4" s="15"/>
       <c r="V4" s="15"/>
       <c r="W4" s="15"/>
@@ -17949,20 +17942,20 @@
       <c r="C5" s="112"/>
       <c r="D5" s="112"/>
       <c r="E5" s="112"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="138"/>
-      <c r="L5" s="138"/>
-      <c r="M5" s="138"/>
-      <c r="N5" s="138"/>
-      <c r="O5" s="138"/>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="138"/>
-      <c r="R5" s="138"/>
-      <c r="S5" s="138"/>
-      <c r="T5" s="138"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="136"/>
+      <c r="T5" s="136"/>
       <c r="U5" s="15"/>
       <c r="V5" s="15"/>
       <c r="W5" s="15"/>
@@ -17976,38 +17969,38 @@
     </row>
     <row r="6" spans="1:32" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="243" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B6" s="109"/>
       <c r="C6" s="109"/>
       <c r="D6" s="109"/>
       <c r="E6" s="109"/>
-      <c r="G6" s="137" t="s">
-        <v>348</v>
-      </c>
-      <c r="H6" s="137">
+      <c r="G6" s="135" t="s">
+        <v>342</v>
+      </c>
+      <c r="H6" s="135">
         <v>1</v>
       </c>
-      <c r="I6" s="137">
+      <c r="I6" s="135">
         <v>2</v>
       </c>
-      <c r="J6" s="137">
+      <c r="J6" s="135">
         <v>7</v>
       </c>
-      <c r="K6" s="137" t="s">
-        <v>349</v>
-      </c>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="137"/>
-      <c r="P6" s="137" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="137"/>
-      <c r="S6" s="137"/>
-      <c r="T6" s="137"/>
+      <c r="K6" s="135" t="s">
+        <v>343</v>
+      </c>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="135"/>
+      <c r="P6" s="135" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="135"/>
+      <c r="S6" s="135"/>
+      <c r="T6" s="135"/>
       <c r="U6" s="15"/>
       <c r="V6" s="15"/>
       <c r="W6" s="15"/>
@@ -18021,30 +18014,30 @@
     </row>
     <row r="7" spans="1:32" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="66" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C7" s="241" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D7" s="242"/>
       <c r="E7" s="242"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
-      <c r="J7" s="138"/>
-      <c r="K7" s="138"/>
-      <c r="L7" s="138"/>
-      <c r="M7" s="138"/>
-      <c r="N7" s="138"/>
-      <c r="O7" s="138"/>
-      <c r="P7" s="138"/>
-      <c r="Q7" s="138"/>
-      <c r="R7" s="138"/>
-      <c r="S7" s="138"/>
-      <c r="T7" s="138"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="136"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
       <c r="U7" s="15"/>
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
@@ -18052,40 +18045,40 @@
     </row>
     <row r="8" spans="1:32" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="230" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B8" s="229">
         <v>3</v>
       </c>
       <c r="C8" s="231" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D8" s="232"/>
       <c r="E8" s="232"/>
       <c r="G8" s="234" t="s">
-        <v>371</v>
-      </c>
-      <c r="H8" s="137">
+        <v>365</v>
+      </c>
+      <c r="H8" s="135">
         <v>1</v>
       </c>
-      <c r="I8" s="137">
+      <c r="I8" s="135">
         <v>1</v>
       </c>
-      <c r="J8" s="137">
+      <c r="J8" s="135">
         <v>7</v>
       </c>
       <c r="K8" s="234" t="s">
-        <v>410</v>
-      </c>
-      <c r="L8" s="137"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="137"/>
-      <c r="O8" s="137"/>
-      <c r="P8" s="137"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="137"/>
-      <c r="S8" s="137"/>
-      <c r="T8" s="137"/>
+        <v>404</v>
+      </c>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="135"/>
+      <c r="P8" s="135"/>
+      <c r="Q8" s="135"/>
+      <c r="R8" s="135"/>
+      <c r="S8" s="135"/>
+      <c r="T8" s="135"/>
       <c r="U8" s="15"/>
       <c r="V8" s="15"/>
       <c r="W8" s="15"/>
@@ -18097,20 +18090,20 @@
       <c r="C9" s="233"/>
       <c r="D9" s="233"/>
       <c r="E9" s="233"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138"/>
-      <c r="N9" s="138"/>
-      <c r="O9" s="138"/>
-      <c r="P9" s="138"/>
-      <c r="Q9" s="138"/>
-      <c r="R9" s="138"/>
-      <c r="S9" s="138"/>
-      <c r="T9" s="138"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="136"/>
+      <c r="O9" s="136"/>
+      <c r="P9" s="136"/>
+      <c r="Q9" s="136"/>
+      <c r="R9" s="136"/>
+      <c r="S9" s="136"/>
+      <c r="T9" s="136"/>
       <c r="U9" s="15"/>
       <c r="V9" s="15"/>
       <c r="W9" s="15"/>
@@ -18118,30 +18111,30 @@
     </row>
     <row r="10" spans="1:32" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A10" s="230" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B10" s="229">
         <v>1</v>
       </c>
       <c r="C10" s="231" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D10" s="232"/>
       <c r="E10" s="232"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="137"/>
-      <c r="P10" s="137"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="137"/>
-      <c r="S10" s="137"/>
-      <c r="T10" s="137"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="135"/>
+      <c r="L10" s="135"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="135"/>
+      <c r="O10" s="135"/>
+      <c r="P10" s="135"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="135"/>
+      <c r="S10" s="135"/>
+      <c r="T10" s="135"/>
       <c r="U10" s="15"/>
       <c r="V10" s="15"/>
       <c r="W10" s="15"/>
@@ -18153,20 +18146,20 @@
       <c r="C11" s="233"/>
       <c r="D11" s="233"/>
       <c r="E11" s="233"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="138"/>
-      <c r="L11" s="138"/>
-      <c r="M11" s="138"/>
-      <c r="N11" s="138"/>
-      <c r="O11" s="138"/>
-      <c r="P11" s="138"/>
-      <c r="Q11" s="138"/>
-      <c r="R11" s="138"/>
-      <c r="S11" s="138"/>
-      <c r="T11" s="138"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="136"/>
+      <c r="P11" s="136"/>
+      <c r="Q11" s="136"/>
+      <c r="R11" s="136"/>
+      <c r="S11" s="136"/>
+      <c r="T11" s="136"/>
       <c r="U11" s="15"/>
       <c r="V11" s="15"/>
       <c r="W11" s="15"/>
@@ -18174,30 +18167,30 @@
     </row>
     <row r="12" spans="1:32" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A12" s="230" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B12" s="229">
         <v>0.5</v>
       </c>
       <c r="C12" s="231" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D12" s="232"/>
       <c r="E12" s="232"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="137"/>
-      <c r="K12" s="137"/>
-      <c r="L12" s="137"/>
-      <c r="M12" s="137"/>
-      <c r="N12" s="137"/>
-      <c r="O12" s="137"/>
-      <c r="P12" s="137"/>
-      <c r="Q12" s="137"/>
-      <c r="R12" s="137"/>
-      <c r="S12" s="137"/>
-      <c r="T12" s="137"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="135"/>
+      <c r="K12" s="135"/>
+      <c r="L12" s="135"/>
+      <c r="M12" s="135"/>
+      <c r="N12" s="135"/>
+      <c r="O12" s="135"/>
+      <c r="P12" s="135"/>
+      <c r="Q12" s="135"/>
+      <c r="R12" s="135"/>
+      <c r="S12" s="135"/>
+      <c r="T12" s="135"/>
       <c r="U12" s="15"/>
       <c r="V12" s="15"/>
       <c r="W12" s="15"/>
@@ -18209,20 +18202,20 @@
       <c r="C13" s="233"/>
       <c r="D13" s="233"/>
       <c r="E13" s="233"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="138"/>
-      <c r="K13" s="138"/>
-      <c r="L13" s="138"/>
-      <c r="M13" s="138"/>
-      <c r="N13" s="138"/>
-      <c r="O13" s="138"/>
-      <c r="P13" s="138"/>
-      <c r="Q13" s="138"/>
-      <c r="R13" s="138"/>
-      <c r="S13" s="138"/>
-      <c r="T13" s="138"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="136"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="136"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="136"/>
+      <c r="P13" s="136"/>
+      <c r="Q13" s="136"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
       <c r="U13" s="15"/>
       <c r="V13" s="15"/>
       <c r="W13" s="15"/>
@@ -18234,20 +18227,20 @@
       <c r="C14" s="227"/>
       <c r="D14" s="227"/>
       <c r="E14" s="227"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="137"/>
-      <c r="O14" s="137"/>
-      <c r="P14" s="137"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="137"/>
-      <c r="S14" s="137"/>
-      <c r="T14" s="137"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="135"/>
+      <c r="O14" s="135"/>
+      <c r="P14" s="135"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="135"/>
+      <c r="S14" s="135"/>
+      <c r="T14" s="135"/>
       <c r="U14" s="15"/>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
@@ -18259,20 +18252,20 @@
       <c r="C15" s="228"/>
       <c r="D15" s="228"/>
       <c r="E15" s="228"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138"/>
-      <c r="K15" s="138"/>
-      <c r="L15" s="138"/>
-      <c r="M15" s="138"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
-      <c r="S15" s="138"/>
-      <c r="T15" s="138"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="136"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="136"/>
+      <c r="P15" s="136"/>
+      <c r="Q15" s="136"/>
+      <c r="R15" s="136"/>
+      <c r="S15" s="136"/>
+      <c r="T15" s="136"/>
       <c r="U15" s="15"/>
       <c r="V15" s="15"/>
       <c r="W15" s="15"/>
@@ -18284,20 +18277,20 @@
       <c r="C16" s="227"/>
       <c r="D16" s="227"/>
       <c r="E16" s="227"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="137"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="137"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="137"/>
-      <c r="O16" s="137"/>
-      <c r="P16" s="137"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="137"/>
-      <c r="S16" s="137"/>
-      <c r="T16" s="137"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="135"/>
+      <c r="P16" s="135"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="135"/>
+      <c r="S16" s="135"/>
+      <c r="T16" s="135"/>
       <c r="U16" s="15"/>
       <c r="V16" s="15"/>
       <c r="W16" s="15"/>
@@ -18309,20 +18302,20 @@
       <c r="C17" s="228"/>
       <c r="D17" s="228"/>
       <c r="E17" s="228"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="138"/>
-      <c r="P17" s="138"/>
-      <c r="Q17" s="138"/>
-      <c r="R17" s="138"/>
-      <c r="S17" s="138"/>
-      <c r="T17" s="138"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="136"/>
+      <c r="P17" s="136"/>
+      <c r="Q17" s="136"/>
+      <c r="R17" s="136"/>
+      <c r="S17" s="136"/>
+      <c r="T17" s="136"/>
       <c r="U17" s="15"/>
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
@@ -18334,20 +18327,20 @@
       <c r="C18" s="227"/>
       <c r="D18" s="227"/>
       <c r="E18" s="227"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="137"/>
-      <c r="O18" s="137"/>
-      <c r="P18" s="137"/>
-      <c r="Q18" s="137"/>
-      <c r="R18" s="137"/>
-      <c r="S18" s="137"/>
-      <c r="T18" s="137"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="135"/>
+      <c r="Q18" s="135"/>
+      <c r="R18" s="135"/>
+      <c r="S18" s="135"/>
+      <c r="T18" s="135"/>
     </row>
     <row r="19" spans="1:24" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="228"/>
@@ -18355,20 +18348,20 @@
       <c r="C19" s="228"/>
       <c r="D19" s="228"/>
       <c r="E19" s="228"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="138"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="138"/>
-      <c r="P19" s="138"/>
-      <c r="Q19" s="138"/>
-      <c r="R19" s="138"/>
-      <c r="S19" s="138"/>
-      <c r="T19" s="138"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
+      <c r="R19" s="136"/>
+      <c r="S19" s="136"/>
+      <c r="T19" s="136"/>
     </row>
     <row r="20" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -18461,10 +18454,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A1" s="187" t="s">
         <v>319</v>
       </c>
@@ -18485,11 +18478,9 @@
       <c r="O1" s="188"/>
       <c r="P1" s="188"/>
       <c r="Q1" s="188"/>
-      <c r="R1" s="188"/>
-      <c r="S1" s="188"/>
-      <c r="T1" s="189"/>
-    </row>
-    <row r="2" spans="1:23" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R1" s="189"/>
+    </row>
+    <row r="2" spans="1:21" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="190"/>
       <c r="B2" s="191"/>
       <c r="C2" s="191"/>
@@ -18506,11 +18497,9 @@
       <c r="O2" s="191"/>
       <c r="P2" s="191"/>
       <c r="Q2" s="191"/>
-      <c r="R2" s="191"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="192"/>
-    </row>
-    <row r="3" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R2" s="192"/>
+    </row>
+    <row r="3" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>156</v>
       </c>
@@ -18521,15 +18510,15 @@
       <c r="D3" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E3" s="183" t="s">
-        <v>321</v>
+      <c r="E3" s="247" t="s">
+        <v>405</v>
       </c>
       <c r="F3" s="183"/>
       <c r="G3" s="1" t="s">
         <v>158</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I3" s="183"/>
       <c r="K3" s="176" t="s">
@@ -18549,19 +18538,13 @@
         <v>187</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="T3" s="65" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="R3" s="65" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>115</v>
       </c>
@@ -18570,24 +18553,24 @@
       </c>
       <c r="C4" s="183"/>
       <c r="D4" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E4" s="2">
+        <v>323</v>
+      </c>
+      <c r="E4" s="183">
         <v>25</v>
       </c>
-      <c r="F4" s="2">
-        <f>E4+R4</f>
-        <v>25</v>
+      <c r="F4" s="183" t="e">
+        <f>E4+#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>162</v>
       </c>
       <c r="H4" s="183" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I4" s="183"/>
       <c r="K4" s="183" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L4" s="183"/>
       <c r="M4" s="2">
@@ -18605,29 +18588,23 @@
       <c r="Q4" s="2">
         <v>20</v>
       </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="64" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R4" s="64" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B5" s="2">
+        <v>326</v>
+      </c>
+      <c r="B5" s="183">
         <v>8</v>
       </c>
-      <c r="C5" s="2">
-        <f>B5+S4</f>
-        <v>8</v>
+      <c r="C5" s="183" t="e">
+        <f>B5+#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E5" s="214">
         <f>E4/10</f>
@@ -18638,12 +18615,12 @@
         <v>185</v>
       </c>
       <c r="H5" s="183">
-        <f>ROUNDDOWN((17/144)*POWER(((F4-Q4)/5-12),2)+3,0)</f>
+        <f>ROUNDDOWN((17/144)*POWER(((E4-Q4)/5-12),2)+3,0)</f>
         <v>17</v>
       </c>
       <c r="I5" s="183"/>
       <c r="K5" s="176" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="L5" s="176"/>
       <c r="M5" s="163" t="s">
@@ -18654,12 +18631,10 @@
       <c r="P5" s="163"/>
       <c r="Q5" s="163"/>
       <c r="R5" s="163"/>
-      <c r="S5" s="163"/>
-      <c r="T5" s="163"/>
-    </row>
-    <row r="6" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="176" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B6" s="163" t="s">
         <v>190</v>
@@ -18679,10 +18654,8 @@
       <c r="P6" s="163"/>
       <c r="Q6" s="163"/>
       <c r="R6" s="163"/>
-      <c r="S6" s="163"/>
-      <c r="T6" s="163"/>
-    </row>
-    <row r="7" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="176"/>
       <c r="B7" s="163"/>
       <c r="C7" s="163"/>
@@ -18693,26 +18666,24 @@
       <c r="H7" s="163"/>
       <c r="I7" s="163"/>
       <c r="K7" s="176" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L7" s="176"/>
       <c r="M7" s="163" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="N7" s="163"/>
       <c r="O7" s="163"/>
       <c r="P7" s="163"/>
       <c r="Q7" s="163"/>
       <c r="R7" s="163"/>
-      <c r="S7" s="163"/>
-      <c r="T7" s="163"/>
-    </row>
-    <row r="8" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="176" t="s">
         <v>175</v>
       </c>
       <c r="B8" s="163" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C8" s="163"/>
       <c r="D8" s="163"/>
@@ -18729,10 +18700,8 @@
       <c r="P8" s="163"/>
       <c r="Q8" s="163"/>
       <c r="R8" s="163"/>
-      <c r="S8" s="163"/>
-      <c r="T8" s="163"/>
-    </row>
-    <row r="9" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="176"/>
       <c r="B9" s="163"/>
       <c r="C9" s="163"/>
@@ -18750,15 +18719,13 @@
       <c r="P9" s="163"/>
       <c r="Q9" s="163"/>
       <c r="R9" s="163"/>
-      <c r="S9" s="163"/>
-      <c r="T9" s="163"/>
-    </row>
-    <row r="10" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="244" t="s">
+        <v>329</v>
+      </c>
+      <c r="B10" s="166" t="s">
         <v>332</v>
-      </c>
-      <c r="B10" s="166" t="s">
-        <v>335</v>
       </c>
       <c r="C10" s="167"/>
       <c r="D10" s="167"/>
@@ -18775,10 +18742,8 @@
       <c r="P10" s="163"/>
       <c r="Q10" s="163"/>
       <c r="R10" s="163"/>
-      <c r="S10" s="163"/>
-      <c r="T10" s="163"/>
-    </row>
-    <row r="11" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="178"/>
       <c r="B11" s="169"/>
       <c r="C11" s="150"/>
@@ -18788,19 +18753,8 @@
       <c r="G11" s="150"/>
       <c r="H11" s="150"/>
       <c r="I11" s="170"/>
-      <c r="K11" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="L11" s="126"/>
-      <c r="M11" s="245"/>
-      <c r="N11" s="245"/>
-      <c r="O11" s="245"/>
-      <c r="P11" s="246"/>
-      <c r="Q11" s="246"/>
-      <c r="R11" s="246"/>
-      <c r="S11" s="246"/>
-    </row>
-    <row r="12" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="178"/>
       <c r="B12" s="169"/>
       <c r="C12" s="150"/>
@@ -18810,23 +18764,8 @@
       <c r="G12" s="150"/>
       <c r="H12" s="150"/>
       <c r="I12" s="170"/>
-      <c r="K12" s="113" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="113"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" s="113"/>
-      <c r="P12" s="113"/>
-      <c r="Q12" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12" s="113"/>
-      <c r="S12" s="113"/>
-    </row>
-    <row r="13" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:21" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="179"/>
       <c r="B13" s="171"/>
       <c r="C13" s="172"/>
@@ -18836,40 +18775,10 @@
       <c r="G13" s="172"/>
       <c r="H13" s="172"/>
       <c r="I13" s="173"/>
-      <c r="K13" s="7">
-        <v>8</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="7">
-        <f>P4</f>
-        <v>8</v>
-      </c>
-      <c r="N13" s="7">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <f>K13+N13</f>
-        <v>8</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S13" s="7">
-        <f>M13+P13</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="132" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -18879,16 +18788,16 @@
       <c r="G14" s="118"/>
       <c r="H14" s="118"/>
       <c r="I14" s="118"/>
-      <c r="W14" s="9"/>
-    </row>
-    <row r="15" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U14" s="9"/>
+    </row>
+    <row r="15" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="113" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="113"/>
       <c r="C15" s="113"/>
       <c r="D15" s="113" t="s">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="E15" s="113"/>
       <c r="F15" s="113"/>
@@ -18898,7 +18807,7 @@
       <c r="H15" s="113"/>
       <c r="I15" s="113"/>
     </row>
-    <row r="16" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>20</v>
       </c>
@@ -18910,47 +18819,48 @@
         <v>20</v>
       </c>
       <c r="D16" s="7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="7">
-        <v>0</v>
+        <f>经历点数与履历!D3/2</f>
+        <v>2.5</v>
       </c>
       <c r="G16" s="7">
         <f>A16+D16</f>
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="7">
         <f>C16+F16</f>
-        <v>20</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="116" t="s">
-        <v>338</v>
-      </c>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
+      <c r="A17" s="125" t="s">
+        <v>333</v>
+      </c>
+      <c r="B17" s="126"/>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
     </row>
     <row r="18" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="113" t="s">
-        <v>339</v>
+        <v>17</v>
       </c>
       <c r="B18" s="113"/>
       <c r="C18" s="113"/>
       <c r="D18" s="113" t="s">
-        <v>340</v>
+        <v>18</v>
       </c>
       <c r="E18" s="113"/>
       <c r="F18" s="113"/>
@@ -18962,34 +18872,34 @@
     </row>
     <row r="19" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="7">
-        <v>6</v>
+        <f>P4</f>
+        <v>8</v>
       </c>
       <c r="D19" s="7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="7">
-        <f>C5</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7">
         <f>A19+D19</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="7">
         <f>C19+F19</f>
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -18997,36 +18907,33 @@
     <row r="22" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="K4:N4 J8 W10 Q4:W4" name="防具区域"/>
+    <protectedRange sqref="K4:N4 J8 U10 Q4:U4" name="防具区域"/>
     <protectedRange sqref="A22:B22 E22:I22" name="防具区域_1"/>
-    <protectedRange sqref="T9:V9" name="防具区域_2"/>
-    <protectedRange sqref="T15:V15" name="防具区域_4"/>
-    <protectedRange sqref="T19:V19" name="防具区域_5"/>
+    <protectedRange sqref="R9:T9" name="防具区域_2"/>
+    <protectedRange sqref="R15:T15" name="防具区域_4"/>
+    <protectedRange sqref="R19:T19" name="防具区域_5"/>
     <protectedRange sqref="I8" name="防具区域_3"/>
     <protectedRange sqref="B3:B6 B8 H3:H5 E3:E5" name="武器区域_1"/>
   </protectedRanges>
-  <mergeCells count="36">
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="K3:L3"/>
+  <mergeCells count="33">
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M5:T6"/>
-    <mergeCell ref="M7:T10"/>
+    <mergeCell ref="M5:R6"/>
+    <mergeCell ref="M7:R10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:I18"/>
-    <mergeCell ref="K1:T2"/>
+    <mergeCell ref="K1:R2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A13"/>
@@ -19038,10 +18945,10 @@
     <mergeCell ref="B10:I13"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="K11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="47" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19530,7 +19437,7 @@
         <v>49</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C9" s="86"/>
       <c r="D9" s="86"/>
@@ -19875,7 +19782,7 @@
         <v>78</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C15" s="108">
         <f ca="1">VLOOKUP(B15,INDIRECT("各种技能"&amp;"!A5:G32"),7,FALSE)</f>
@@ -20008,7 +19915,7 @@
         <v>92</v>
       </c>
       <c r="B17" s="107" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C17" s="107"/>
       <c r="D17" s="107"/>
@@ -20314,7 +20221,7 @@
       </c>
       <c r="K22" s="42">
         <f t="array" aca="1" ref="K22" ca="1">INDIRECT("坐骑"&amp;"!S13")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M22" s="58" t="s">
         <v>109</v>
@@ -20914,880 +20821,880 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="140" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142" t="s">
-        <v>403</v>
-      </c>
-      <c r="N1" s="142"/>
-      <c r="P1" s="143" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140" t="s">
+        <v>397</v>
+      </c>
+      <c r="N1" s="140"/>
+      <c r="P1" s="141" t="s">
         <v>121</v>
       </c>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
     </row>
     <row r="2" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="142"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
-      <c r="N2" s="142"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="143"/>
-      <c r="Y2" s="143"/>
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="141"/>
+      <c r="W2" s="141"/>
+      <c r="X2" s="141"/>
+      <c r="Y2" s="141"/>
     </row>
     <row r="3" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
+      <c r="A3" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="140">
+      <c r="B3" s="142"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="138">
         <f>SUMIF(E9:H591,"&gt;=0",E9:H591)</f>
         <v>5</v>
       </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="146" t="s">
-        <v>370</v>
-      </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="140">
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="144" t="s">
+        <v>364</v>
+      </c>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="138">
         <f>1+INT(D3/8)</f>
         <v>1</v>
       </c>
-      <c r="K3" s="140"/>
-      <c r="L3" s="140"/>
-      <c r="M3" s="135" t="s">
-        <v>404</v>
-      </c>
-      <c r="N3" s="135" t="s">
-        <v>405</v>
-      </c>
-      <c r="P3" s="139" t="s">
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="145" t="s">
+        <v>398</v>
+      </c>
+      <c r="N3" s="145" t="s">
+        <v>399</v>
+      </c>
+      <c r="P3" s="137" t="s">
         <v>123</v>
       </c>
-      <c r="Q3" s="139"/>
-      <c r="R3" s="139"/>
-      <c r="S3" s="139"/>
-      <c r="T3" s="139"/>
-      <c r="U3" s="139"/>
-      <c r="V3" s="139"/>
-      <c r="W3" s="139"/>
-      <c r="X3" s="139"/>
-      <c r="Y3" s="139"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="137"/>
+      <c r="S3" s="137"/>
+      <c r="T3" s="137"/>
+      <c r="U3" s="137"/>
+      <c r="V3" s="137"/>
+      <c r="W3" s="137"/>
+      <c r="X3" s="137"/>
+      <c r="Y3" s="137"/>
     </row>
     <row r="4" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="145"/>
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="141"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="141"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="136"/>
-      <c r="P4" s="139"/>
-      <c r="Q4" s="139"/>
-      <c r="R4" s="139"/>
-      <c r="S4" s="139"/>
-      <c r="T4" s="139"/>
-      <c r="U4" s="139"/>
-      <c r="V4" s="139"/>
-      <c r="W4" s="139"/>
-      <c r="X4" s="139"/>
-      <c r="Y4" s="139"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
+      <c r="W4" s="137"/>
+      <c r="X4" s="137"/>
+      <c r="Y4" s="137"/>
     </row>
     <row r="5" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="140">
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="138">
         <f>D3-J5</f>
         <v>5</v>
       </c>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="144" t="s">
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="140">
+      <c r="H5" s="142"/>
+      <c r="I5" s="142"/>
+      <c r="J5" s="138">
         <f>E11</f>
         <v>0</v>
       </c>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="138"/>
       <c r="M5" s="133" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="N5" s="133" t="s">
-        <v>407</v>
-      </c>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="139"/>
-      <c r="R5" s="139"/>
-      <c r="S5" s="139"/>
-      <c r="T5" s="139"/>
-      <c r="U5" s="139"/>
-      <c r="V5" s="139"/>
-      <c r="W5" s="139"/>
-      <c r="X5" s="139"/>
-      <c r="Y5" s="139"/>
+        <v>401</v>
+      </c>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="137"/>
+      <c r="R5" s="137"/>
+      <c r="S5" s="137"/>
+      <c r="T5" s="137"/>
+      <c r="U5" s="137"/>
+      <c r="V5" s="137"/>
+      <c r="W5" s="137"/>
+      <c r="X5" s="137"/>
+      <c r="Y5" s="137"/>
     </row>
     <row r="6" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="145"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="141"/>
-      <c r="E6" s="141"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="145"/>
-      <c r="I6" s="145"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141"/>
+      <c r="A6" s="143"/>
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
       <c r="M6" s="134"/>
       <c r="N6" s="134"/>
-      <c r="P6" s="139"/>
-      <c r="Q6" s="139"/>
-      <c r="R6" s="139"/>
-      <c r="S6" s="139"/>
-      <c r="T6" s="139"/>
-      <c r="U6" s="139"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="139"/>
-      <c r="X6" s="139"/>
-      <c r="Y6" s="139"/>
+      <c r="P6" s="137"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="137"/>
+      <c r="S6" s="137"/>
+      <c r="T6" s="137"/>
+      <c r="U6" s="137"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="137"/>
+      <c r="X6" s="137"/>
+      <c r="Y6" s="137"/>
     </row>
     <row r="7" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="140" t="s">
+      <c r="A7" s="138" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140" t="s">
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140" t="s">
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
       <c r="M7" s="133"/>
       <c r="N7" s="133"/>
-      <c r="P7" s="139"/>
-      <c r="Q7" s="139"/>
-      <c r="R7" s="139"/>
-      <c r="S7" s="139"/>
-      <c r="T7" s="139"/>
-      <c r="U7" s="139"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="139"/>
-      <c r="X7" s="139"/>
-      <c r="Y7" s="139"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="137"/>
+      <c r="U7" s="137"/>
+      <c r="V7" s="137"/>
+      <c r="W7" s="137"/>
+      <c r="X7" s="137"/>
+      <c r="Y7" s="137"/>
     </row>
     <row r="8" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="141"/>
-      <c r="B8" s="141"/>
-      <c r="C8" s="141"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
+      <c r="A8" s="139"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
       <c r="M8" s="134"/>
       <c r="N8" s="134"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="139"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="139"/>
-      <c r="T8" s="139"/>
-      <c r="U8" s="139"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="139"/>
-      <c r="X8" s="139"/>
-      <c r="Y8" s="139"/>
+      <c r="P8" s="137"/>
+      <c r="Q8" s="137"/>
+      <c r="R8" s="137"/>
+      <c r="S8" s="137"/>
+      <c r="T8" s="137"/>
+      <c r="U8" s="137"/>
+      <c r="V8" s="137"/>
+      <c r="W8" s="137"/>
+      <c r="X8" s="137"/>
+      <c r="Y8" s="137"/>
     </row>
     <row r="9" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="137" t="s">
+      <c r="A9" s="135" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="137"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137">
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135">
         <v>5</v>
       </c>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137">
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135">
         <f>E9</f>
         <v>5</v>
       </c>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
       <c r="M9" s="133"/>
       <c r="N9" s="133"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139"/>
-      <c r="T9" s="139"/>
-      <c r="U9" s="139"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="139"/>
-      <c r="X9" s="139"/>
-      <c r="Y9" s="139"/>
+      <c r="P9" s="137"/>
+      <c r="Q9" s="137"/>
+      <c r="R9" s="137"/>
+      <c r="S9" s="137"/>
+      <c r="T9" s="137"/>
+      <c r="U9" s="137"/>
+      <c r="V9" s="137"/>
+      <c r="W9" s="137"/>
+      <c r="X9" s="137"/>
+      <c r="Y9" s="137"/>
     </row>
     <row r="10" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="138"/>
-      <c r="B10" s="138"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138"/>
+      <c r="A10" s="136"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="136"/>
+      <c r="E10" s="136"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="136"/>
+      <c r="H10" s="136"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="136"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
       <c r="M10" s="134"/>
       <c r="N10" s="134"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="139"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
-      <c r="T10" s="139"/>
-      <c r="U10" s="139"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="139"/>
-      <c r="X10" s="139"/>
-      <c r="Y10" s="139"/>
+      <c r="P10" s="137"/>
+      <c r="Q10" s="137"/>
+      <c r="R10" s="137"/>
+      <c r="S10" s="137"/>
+      <c r="T10" s="137"/>
+      <c r="U10" s="137"/>
+      <c r="V10" s="137"/>
+      <c r="W10" s="137"/>
+      <c r="X10" s="137"/>
+      <c r="Y10" s="137"/>
     </row>
     <row r="11" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137">
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135">
         <f>IF((240-SUM(总表!G3,总表!G5,总表!G7,总表!G9,总表!G11,总表!G13))/5&gt;0,(240-SUM(总表!G3,总表!G5,总表!G7,总表!G9,总表!G11,总表!G13))/5,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137">
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135">
         <f>E11+I9</f>
         <v>5</v>
       </c>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
+      <c r="L11" s="135"/>
       <c r="M11" s="133"/>
       <c r="N11" s="133"/>
-      <c r="P11" s="139"/>
-      <c r="Q11" s="139"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="139"/>
-      <c r="T11" s="139"/>
-      <c r="U11" s="139"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="139"/>
-      <c r="X11" s="139"/>
-      <c r="Y11" s="139"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="137"/>
+      <c r="U11" s="137"/>
+      <c r="V11" s="137"/>
+      <c r="W11" s="137"/>
+      <c r="X11" s="137"/>
+      <c r="Y11" s="137"/>
     </row>
     <row r="12" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="138"/>
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="138"/>
-      <c r="K12" s="138"/>
-      <c r="L12" s="138"/>
+      <c r="A12" s="136"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="136"/>
       <c r="M12" s="134"/>
       <c r="N12" s="134"/>
-      <c r="P12" s="139"/>
-      <c r="Q12" s="139"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
-      <c r="T12" s="139"/>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
-      <c r="X12" s="139"/>
-      <c r="Y12" s="139"/>
+      <c r="P12" s="137"/>
+      <c r="Q12" s="137"/>
+      <c r="R12" s="137"/>
+      <c r="S12" s="137"/>
+      <c r="T12" s="137"/>
+      <c r="U12" s="137"/>
+      <c r="V12" s="137"/>
+      <c r="W12" s="137"/>
+      <c r="X12" s="137"/>
+      <c r="Y12" s="137"/>
     </row>
     <row r="13" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="135" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137">
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135">
         <v>0</v>
       </c>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137">
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135">
         <f t="shared" ref="I13" si="0">E13+I11</f>
         <v>5</v>
       </c>
-      <c r="J13" s="137"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
       <c r="M13" s="133"/>
       <c r="N13" s="133"/>
-      <c r="P13" s="139"/>
-      <c r="Q13" s="139"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
-      <c r="T13" s="139"/>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="139"/>
-      <c r="X13" s="139"/>
-      <c r="Y13" s="139"/>
+      <c r="P13" s="137"/>
+      <c r="Q13" s="137"/>
+      <c r="R13" s="137"/>
+      <c r="S13" s="137"/>
+      <c r="T13" s="137"/>
+      <c r="U13" s="137"/>
+      <c r="V13" s="137"/>
+      <c r="W13" s="137"/>
+      <c r="X13" s="137"/>
+      <c r="Y13" s="137"/>
     </row>
     <row r="14" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="138"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
+      <c r="A14" s="136"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
       <c r="M14" s="134"/>
       <c r="N14" s="134"/>
-      <c r="P14" s="139"/>
-      <c r="Q14" s="139"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="139"/>
-      <c r="T14" s="139"/>
-      <c r="U14" s="139"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="139"/>
-      <c r="X14" s="139"/>
-      <c r="Y14" s="139"/>
+      <c r="P14" s="137"/>
+      <c r="Q14" s="137"/>
+      <c r="R14" s="137"/>
+      <c r="S14" s="137"/>
+      <c r="T14" s="137"/>
+      <c r="U14" s="137"/>
+      <c r="V14" s="137"/>
+      <c r="W14" s="137"/>
+      <c r="X14" s="137"/>
+      <c r="Y14" s="137"/>
     </row>
     <row r="15" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="137" t="s">
-        <v>346</v>
-      </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137">
+      <c r="A15" s="135" t="s">
+        <v>340</v>
+      </c>
+      <c r="B15" s="135"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135">
         <v>-3</v>
       </c>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137">
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135">
         <f t="shared" ref="I15" si="1">E15+I13</f>
         <v>2</v>
       </c>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
       <c r="M15" s="133"/>
       <c r="N15" s="133"/>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
-      <c r="U15" s="139"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="139"/>
-      <c r="X15" s="139"/>
-      <c r="Y15" s="139"/>
+      <c r="P15" s="137"/>
+      <c r="Q15" s="137"/>
+      <c r="R15" s="137"/>
+      <c r="S15" s="137"/>
+      <c r="T15" s="137"/>
+      <c r="U15" s="137"/>
+      <c r="V15" s="137"/>
+      <c r="W15" s="137"/>
+      <c r="X15" s="137"/>
+      <c r="Y15" s="137"/>
     </row>
     <row r="16" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="138"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138"/>
+      <c r="A16" s="136"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
       <c r="M16" s="134"/>
       <c r="N16" s="134"/>
-      <c r="P16" s="139"/>
-      <c r="Q16" s="139"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="139"/>
-      <c r="T16" s="139"/>
-      <c r="U16" s="139"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="139"/>
-      <c r="X16" s="139"/>
-      <c r="Y16" s="139"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="137"/>
+      <c r="U16" s="137"/>
+      <c r="V16" s="137"/>
+      <c r="W16" s="137"/>
+      <c r="X16" s="137"/>
+      <c r="Y16" s="137"/>
     </row>
     <row r="17" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="137" t="s">
+      <c r="A17" s="135" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="137"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137">
+      <c r="B17" s="135"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135">
         <v>-2</v>
       </c>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="137">
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135">
         <f t="shared" ref="I17" si="2">E17+I15</f>
         <v>0</v>
       </c>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="135"/>
+      <c r="L17" s="135"/>
       <c r="M17" s="133"/>
       <c r="N17" s="133"/>
-      <c r="P17" s="139"/>
-      <c r="Q17" s="139"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="139"/>
-      <c r="T17" s="139"/>
-      <c r="U17" s="139"/>
-      <c r="V17" s="139"/>
-      <c r="W17" s="139"/>
-      <c r="X17" s="139"/>
-      <c r="Y17" s="139"/>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="137"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="137"/>
+      <c r="U17" s="137"/>
+      <c r="V17" s="137"/>
+      <c r="W17" s="137"/>
+      <c r="X17" s="137"/>
+      <c r="Y17" s="137"/>
     </row>
     <row r="18" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="138"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
+      <c r="A18" s="136"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="136"/>
+      <c r="E18" s="136"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="136"/>
+      <c r="H18" s="136"/>
+      <c r="I18" s="136"/>
+      <c r="J18" s="136"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="136"/>
       <c r="M18" s="134"/>
       <c r="N18" s="134"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
-      <c r="T18" s="139"/>
-      <c r="U18" s="139"/>
-      <c r="V18" s="139"/>
-      <c r="W18" s="139"/>
-      <c r="X18" s="139"/>
-      <c r="Y18" s="139"/>
+      <c r="P18" s="137"/>
+      <c r="Q18" s="137"/>
+      <c r="R18" s="137"/>
+      <c r="S18" s="137"/>
+      <c r="T18" s="137"/>
+      <c r="U18" s="137"/>
+      <c r="V18" s="137"/>
+      <c r="W18" s="137"/>
+      <c r="X18" s="137"/>
+      <c r="Y18" s="137"/>
     </row>
     <row r="19" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="137"/>
-      <c r="B19" s="137"/>
-      <c r="C19" s="137"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
-      <c r="H19" s="137"/>
-      <c r="I19" s="137">
+      <c r="A19" s="135"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135">
         <f t="shared" ref="I19" si="3">E19+I17</f>
         <v>0</v>
       </c>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="135"/>
+      <c r="L19" s="135"/>
       <c r="M19" s="133"/>
       <c r="N19" s="133"/>
-      <c r="P19" s="139"/>
-      <c r="Q19" s="139"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="139"/>
-      <c r="T19" s="139"/>
-      <c r="U19" s="139"/>
-      <c r="V19" s="139"/>
-      <c r="W19" s="139"/>
-      <c r="X19" s="139"/>
-      <c r="Y19" s="139"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="137"/>
+      <c r="R19" s="137"/>
+      <c r="S19" s="137"/>
+      <c r="T19" s="137"/>
+      <c r="U19" s="137"/>
+      <c r="V19" s="137"/>
+      <c r="W19" s="137"/>
+      <c r="X19" s="137"/>
+      <c r="Y19" s="137"/>
     </row>
     <row r="20" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="138"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138"/>
+      <c r="A20" s="136"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
       <c r="M20" s="134"/>
       <c r="N20" s="134"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="139"/>
-      <c r="T20" s="139"/>
-      <c r="U20" s="139"/>
-      <c r="V20" s="139"/>
-      <c r="W20" s="139"/>
-      <c r="X20" s="139"/>
-      <c r="Y20" s="139"/>
+      <c r="P20" s="137"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="137"/>
+      <c r="S20" s="137"/>
+      <c r="T20" s="137"/>
+      <c r="U20" s="137"/>
+      <c r="V20" s="137"/>
+      <c r="W20" s="137"/>
+      <c r="X20" s="137"/>
+      <c r="Y20" s="137"/>
     </row>
     <row r="21" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="137"/>
-      <c r="B21" s="137"/>
-      <c r="C21" s="137"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="137"/>
-      <c r="I21" s="137">
+      <c r="A21" s="135"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="135">
         <f t="shared" ref="I21" si="4">E21+I19</f>
         <v>0</v>
       </c>
-      <c r="J21" s="137"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="137"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="135"/>
       <c r="M21" s="133"/>
       <c r="N21" s="133"/>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="139"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
-      <c r="T21" s="139"/>
-      <c r="U21" s="139"/>
-      <c r="V21" s="139"/>
-      <c r="W21" s="139"/>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="139"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="137"/>
+      <c r="R21" s="137"/>
+      <c r="S21" s="137"/>
+      <c r="T21" s="137"/>
+      <c r="U21" s="137"/>
+      <c r="V21" s="137"/>
+      <c r="W21" s="137"/>
+      <c r="X21" s="137"/>
+      <c r="Y21" s="137"/>
     </row>
     <row r="22" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="138"/>
-      <c r="B22" s="138"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
+      <c r="A22" s="136"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
       <c r="M22" s="134"/>
       <c r="N22" s="134"/>
-      <c r="P22" s="139"/>
-      <c r="Q22" s="139"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="139"/>
-      <c r="T22" s="139"/>
-      <c r="U22" s="139"/>
-      <c r="V22" s="139"/>
-      <c r="W22" s="139"/>
-      <c r="X22" s="139"/>
-      <c r="Y22" s="139"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="137"/>
+      <c r="S22" s="137"/>
+      <c r="T22" s="137"/>
+      <c r="U22" s="137"/>
+      <c r="V22" s="137"/>
+      <c r="W22" s="137"/>
+      <c r="X22" s="137"/>
+      <c r="Y22" s="137"/>
     </row>
     <row r="23" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="137"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="137"/>
-      <c r="I23" s="137">
+      <c r="A23" s="135"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="135"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135">
         <f t="shared" ref="I23" si="5">E23+I21</f>
         <v>0</v>
       </c>
-      <c r="J23" s="137"/>
-      <c r="K23" s="137"/>
-      <c r="L23" s="137"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
       <c r="M23" s="133"/>
       <c r="N23" s="133"/>
-      <c r="P23" s="139"/>
-      <c r="Q23" s="139"/>
-      <c r="R23" s="139"/>
-      <c r="S23" s="139"/>
-      <c r="T23" s="139"/>
-      <c r="U23" s="139"/>
-      <c r="V23" s="139"/>
-      <c r="W23" s="139"/>
-      <c r="X23" s="139"/>
-      <c r="Y23" s="139"/>
+      <c r="P23" s="137"/>
+      <c r="Q23" s="137"/>
+      <c r="R23" s="137"/>
+      <c r="S23" s="137"/>
+      <c r="T23" s="137"/>
+      <c r="U23" s="137"/>
+      <c r="V23" s="137"/>
+      <c r="W23" s="137"/>
+      <c r="X23" s="137"/>
+      <c r="Y23" s="137"/>
     </row>
     <row r="24" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="138"/>
-      <c r="B24" s="138"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="138"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="138"/>
+      <c r="A24" s="136"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="136"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="136"/>
       <c r="M24" s="134"/>
       <c r="N24" s="134"/>
-      <c r="P24" s="139"/>
-      <c r="Q24" s="139"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139"/>
-      <c r="T24" s="139"/>
-      <c r="U24" s="139"/>
-      <c r="V24" s="139"/>
-      <c r="W24" s="139"/>
-      <c r="X24" s="139"/>
-      <c r="Y24" s="139"/>
+      <c r="P24" s="137"/>
+      <c r="Q24" s="137"/>
+      <c r="R24" s="137"/>
+      <c r="S24" s="137"/>
+      <c r="T24" s="137"/>
+      <c r="U24" s="137"/>
+      <c r="V24" s="137"/>
+      <c r="W24" s="137"/>
+      <c r="X24" s="137"/>
+      <c r="Y24" s="137"/>
     </row>
     <row r="25" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="137"/>
-      <c r="B25" s="137"/>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137">
+      <c r="A25" s="135"/>
+      <c r="B25" s="135"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="135">
         <f t="shared" ref="I25" si="6">E25+I23</f>
         <v>0</v>
       </c>
-      <c r="J25" s="137"/>
-      <c r="K25" s="137"/>
-      <c r="L25" s="137"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
+      <c r="L25" s="135"/>
       <c r="M25" s="133"/>
       <c r="N25" s="133"/>
-      <c r="P25" s="139"/>
-      <c r="Q25" s="139"/>
-      <c r="R25" s="139"/>
-      <c r="S25" s="139"/>
-      <c r="T25" s="139"/>
-      <c r="U25" s="139"/>
-      <c r="V25" s="139"/>
-      <c r="W25" s="139"/>
-      <c r="X25" s="139"/>
-      <c r="Y25" s="139"/>
+      <c r="P25" s="137"/>
+      <c r="Q25" s="137"/>
+      <c r="R25" s="137"/>
+      <c r="S25" s="137"/>
+      <c r="T25" s="137"/>
+      <c r="U25" s="137"/>
+      <c r="V25" s="137"/>
+      <c r="W25" s="137"/>
+      <c r="X25" s="137"/>
+      <c r="Y25" s="137"/>
     </row>
     <row r="26" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="138"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="138"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="138"/>
+      <c r="A26" s="136"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="136"/>
       <c r="M26" s="134"/>
       <c r="N26" s="134"/>
-      <c r="P26" s="139"/>
-      <c r="Q26" s="139"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="139"/>
-      <c r="T26" s="139"/>
-      <c r="U26" s="139"/>
-      <c r="V26" s="139"/>
-      <c r="W26" s="139"/>
-      <c r="X26" s="139"/>
-      <c r="Y26" s="139"/>
+      <c r="P26" s="137"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="137"/>
+      <c r="S26" s="137"/>
+      <c r="T26" s="137"/>
+      <c r="U26" s="137"/>
+      <c r="V26" s="137"/>
+      <c r="W26" s="137"/>
+      <c r="X26" s="137"/>
+      <c r="Y26" s="137"/>
     </row>
     <row r="27" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="137"/>
-      <c r="B27" s="137"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="137"/>
-      <c r="I27" s="137">
+      <c r="A27" s="135"/>
+      <c r="B27" s="135"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="135">
         <f t="shared" ref="I27" si="7">E27+I25</f>
         <v>0</v>
       </c>
-      <c r="J27" s="137"/>
-      <c r="K27" s="137"/>
-      <c r="L27" s="137"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="135"/>
       <c r="M27" s="133"/>
       <c r="N27" s="133"/>
-      <c r="P27" s="139"/>
-      <c r="Q27" s="139"/>
-      <c r="R27" s="139"/>
-      <c r="S27" s="139"/>
-      <c r="T27" s="139"/>
-      <c r="U27" s="139"/>
-      <c r="V27" s="139"/>
-      <c r="W27" s="139"/>
-      <c r="X27" s="139"/>
-      <c r="Y27" s="139"/>
+      <c r="P27" s="137"/>
+      <c r="Q27" s="137"/>
+      <c r="R27" s="137"/>
+      <c r="S27" s="137"/>
+      <c r="T27" s="137"/>
+      <c r="U27" s="137"/>
+      <c r="V27" s="137"/>
+      <c r="W27" s="137"/>
+      <c r="X27" s="137"/>
+      <c r="Y27" s="137"/>
     </row>
     <row r="28" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="138"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
+      <c r="A28" s="136"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="136"/>
       <c r="M28" s="134"/>
       <c r="N28" s="134"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="139"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="139"/>
-      <c r="T28" s="139"/>
-      <c r="U28" s="139"/>
-      <c r="V28" s="139"/>
-      <c r="W28" s="139"/>
-      <c r="X28" s="139"/>
-      <c r="Y28" s="139"/>
+      <c r="P28" s="137"/>
+      <c r="Q28" s="137"/>
+      <c r="R28" s="137"/>
+      <c r="S28" s="137"/>
+      <c r="T28" s="137"/>
+      <c r="U28" s="137"/>
+      <c r="V28" s="137"/>
+      <c r="W28" s="137"/>
+      <c r="X28" s="137"/>
+      <c r="Y28" s="137"/>
     </row>
     <row r="29" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="137"/>
-      <c r="B29" s="137"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="137">
+      <c r="A29" s="135"/>
+      <c r="B29" s="135"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="135"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="135"/>
+      <c r="I29" s="135">
         <f t="shared" ref="I29" si="8">E29+I27</f>
         <v>0</v>
       </c>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
+      <c r="L29" s="135"/>
       <c r="M29" s="133"/>
       <c r="N29" s="133"/>
-      <c r="P29" s="139"/>
-      <c r="Q29" s="139"/>
-      <c r="R29" s="139"/>
-      <c r="S29" s="139"/>
-      <c r="T29" s="139"/>
-      <c r="U29" s="139"/>
-      <c r="V29" s="139"/>
-      <c r="W29" s="139"/>
-      <c r="X29" s="139"/>
-      <c r="Y29" s="139"/>
+      <c r="P29" s="137"/>
+      <c r="Q29" s="137"/>
+      <c r="R29" s="137"/>
+      <c r="S29" s="137"/>
+      <c r="T29" s="137"/>
+      <c r="U29" s="137"/>
+      <c r="V29" s="137"/>
+      <c r="W29" s="137"/>
+      <c r="X29" s="137"/>
+      <c r="Y29" s="137"/>
     </row>
     <row r="30" spans="1:25" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="138"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="138"/>
+      <c r="A30" s="136"/>
+      <c r="B30" s="136"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
       <c r="M30" s="134"/>
       <c r="N30" s="134"/>
-      <c r="P30" s="139"/>
-      <c r="Q30" s="139"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="139"/>
-      <c r="T30" s="139"/>
-      <c r="U30" s="139"/>
-      <c r="V30" s="139"/>
-      <c r="W30" s="139"/>
-      <c r="X30" s="139"/>
-      <c r="Y30" s="139"/>
+      <c r="P30" s="137"/>
+      <c r="Q30" s="137"/>
+      <c r="R30" s="137"/>
+      <c r="S30" s="137"/>
+      <c r="T30" s="137"/>
+      <c r="U30" s="137"/>
+      <c r="V30" s="137"/>
+      <c r="W30" s="137"/>
+      <c r="X30" s="137"/>
+      <c r="Y30" s="137"/>
     </row>
     <row r="31" spans="1:25" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:25" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -21823,6 +21730,7 @@
     <mergeCell ref="J3:L4"/>
     <mergeCell ref="M1:N2"/>
     <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="A13:D14"/>
     <mergeCell ref="E13:H14"/>
     <mergeCell ref="I13:L14"/>
@@ -21857,7 +21765,6 @@
     <mergeCell ref="A25:D26"/>
     <mergeCell ref="E25:H26"/>
     <mergeCell ref="I25:L26"/>
-    <mergeCell ref="N3:N4"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="M7:M8"/>
@@ -22777,7 +22684,7 @@
       <c r="F4" s="148"/>
       <c r="G4" s="148"/>
       <c r="I4" s="152" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="J4" s="148"/>
       <c r="K4" s="148"/>
@@ -23512,7 +23419,7 @@
         <v>172</v>
       </c>
       <c r="D6" s="174" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E6" s="163"/>
       <c r="F6" s="163"/>
@@ -23977,7 +23884,7 @@
     </row>
     <row r="3" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="184" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B3" s="176" t="s">
         <v>157</v>
@@ -24067,7 +23974,7 @@
     </row>
     <row r="5" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="184" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B5" s="183" t="s">
         <v>189</v>
@@ -24121,7 +24028,7 @@
     </row>
     <row r="7" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="184" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B7" s="176" t="s">
         <v>157</v>
@@ -24211,7 +24118,7 @@
     </row>
     <row r="9" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="184" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B9" s="183" t="s">
         <v>191</v>
@@ -24265,7 +24172,7 @@
     </row>
     <row r="11" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="184" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B11" s="176" t="s">
         <v>157</v>
@@ -24357,7 +24264,7 @@
     </row>
     <row r="13" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="184" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B13" s="183" t="s">
         <v>192</v>
@@ -24411,7 +24318,7 @@
     </row>
     <row r="15" spans="1:24" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="184" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B15" s="176" t="s">
         <v>157</v>
@@ -24501,7 +24408,7 @@
     </row>
     <row r="17" spans="1:23" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="184" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B17" s="183" t="s">
         <v>193</v>
@@ -25060,16 +24967,16 @@
       <c r="X7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="2" t="e">
         <f>坐骑!F4</f>
-        <v>25</v>
+        <v>#REF!</v>
       </c>
       <c r="Z7" s="205"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
-      <c r="AC7" s="3">
+      <c r="AC7" s="3" t="e">
         <f>IF(SUM(Y7,Z6,AA7)&lt;=50,SUM(Y7,Z6,AA7),IF(SUM(Y7,Z6,AA7)&lt;=80,(SUM(Y7,Z6,AA7)-50)*0.7+50,(SUM(Y7,Z6,AA7)-80)*0.4+71))+AB7</f>
-        <v>26</v>
+        <v>#REF!</v>
       </c>
       <c r="AD7" s="205"/>
       <c r="AE7" s="205"/>
@@ -25577,7 +25484,7 @@
       <c r="I14" s="202"/>
       <c r="J14" s="203"/>
       <c r="L14" s="67" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>31</v>
@@ -26061,7 +25968,7 @@
         <v>23</v>
       </c>
       <c r="J20" s="2" t="str">
-        <f t="shared" ref="J20:J32" si="18">IF(D20&lt;10,"6",IF(D20&lt;20,"9",IF(D20&lt;30,"12",18)))</f>
+        <f t="shared" ref="J20:J23" si="18">IF(D20&lt;10,"6",IF(D20&lt;20,"9",IF(D20&lt;30,"12",18)))</f>
         <v>6</v>
       </c>
       <c r="L20" s="2" t="s">
@@ -26129,7 +26036,7 @@
         <v>46</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" ref="C21:C25" ca="1" si="19">LOOKUP(INDIRECT("rc[-1]",),INDIRECT("总表"&amp;"!A29:A34"),INDIRECT("总表"&amp;"!B29:B34"))</f>
+        <f t="shared" ref="C21:C23" ca="1" si="19">LOOKUP(INDIRECT("rc[-1]",),INDIRECT("总表"&amp;"!A29:A34"),INDIRECT("总表"&amp;"!B29:B34"))</f>
         <v>30</v>
       </c>
       <c r="D21" s="2">
@@ -26138,7 +26045,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="3">
-        <f t="shared" ref="G21:G25" ca="1" si="20">IF(SUM(C21:E21)&lt;=50,SUM(C21:E21),IF(SUM(C21:E21)&lt;=80,(SUM(C21:E21)-50)*0.7+50,(SUM(C21:E21)-80)*0.4+71))+F21</f>
+        <f t="shared" ref="G21:G23" ca="1" si="20">IF(SUM(C21:E21)&lt;=50,SUM(C21:E21),IF(SUM(C21:E21)&lt;=80,(SUM(C21:E21)-50)*0.7+50,(SUM(C21:E21)-80)*0.4+71))+F21</f>
         <v>31</v>
       </c>
       <c r="H21" s="2">
@@ -26280,7 +26187,7 @@
     </row>
     <row r="23" spans="1:32" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="64" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>46</v>
@@ -27007,7 +26914,7 @@
     </row>
     <row r="35" spans="12:21" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="201" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="M35" s="202"/>
       <c r="N35" s="202"/>
@@ -27021,10 +26928,10 @@
     </row>
     <row r="36" spans="12:21" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L36" s="64" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M36" s="64" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="N36" s="2">
         <f ca="1">LOOKUP(INDIRECT("rc[-1]",),INDIRECT("总表"&amp;"!A29:A34"),INDIRECT("总表"&amp;"!B29:B34"))</f>
@@ -27052,7 +26959,7 @@
     </row>
     <row r="37" spans="12:21" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L37" s="64" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>11</v>
@@ -27083,10 +26990,10 @@
     </row>
     <row r="38" spans="12:21" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L38" s="64" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="M38" s="64" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="N38" s="2">
         <f ca="1">LOOKUP(INDIRECT("rc[-1]",),INDIRECT("总表"&amp;"!A29:A34"),INDIRECT("总表"&amp;"!B29:B34"))</f>
@@ -27114,10 +27021,10 @@
     </row>
     <row r="39" spans="12:21" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L39" s="64" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="M39" s="64" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="N39" s="2">
         <f ca="1">LOOKUP(INDIRECT("rc[-1]",),INDIRECT("总表"&amp;"!A29:A34"),INDIRECT("总表"&amp;"!B29:B34"))</f>
@@ -27145,10 +27052,10 @@
     </row>
     <row r="40" spans="12:21" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L40" s="64" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M40" s="64" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="N40" s="2">
         <f ca="1">LOOKUP(INDIRECT("rc[-1]",),INDIRECT("总表"&amp;"!A29:A34"),INDIRECT("总表"&amp;"!B29:B34"))</f>
@@ -27326,7 +27233,7 @@
       <c r="P5" s="167"/>
       <c r="Q5" s="168"/>
       <c r="R5" s="213" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="S5" s="167"/>
       <c r="T5" s="167"/>
@@ -27381,14 +27288,14 @@
       <c r="K7" s="167"/>
       <c r="L7" s="168"/>
       <c r="M7" s="213" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="N7" s="167"/>
       <c r="O7" s="167"/>
       <c r="P7" s="167"/>
       <c r="Q7" s="168"/>
       <c r="R7" s="213" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="S7" s="167"/>
       <c r="T7" s="167"/>
@@ -27487,7 +27394,7 @@
         <v>116</v>
       </c>
       <c r="C11" s="207" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D11" s="208"/>
       <c r="E11" s="208"/>
@@ -27508,7 +27415,7 @@
       <c r="P11" s="167"/>
       <c r="Q11" s="168"/>
       <c r="R11" s="166" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="S11" s="167"/>
       <c r="T11" s="167"/>
